--- a/Team-Data/2013-14/4-8-2013-14.xlsx
+++ b/Team-Data/2013-14/4-8-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.442</v>
+        <v>0.447</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L2" t="n">
         <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O2" t="n">
         <v>16.9</v>
@@ -700,19 +767,19 @@
         <v>21.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R2" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>31.2</v>
       </c>
       <c r="T2" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="U2" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="V2" t="n">
         <v>15.4</v>
@@ -721,7 +788,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
@@ -736,10 +803,10 @@
         <v>101.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
@@ -769,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="n">
         <v>20</v>
@@ -796,7 +863,7 @@
         <v>26</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>26</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
@@ -972,10 +1039,10 @@
         <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
         <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.553</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,10 +1110,10 @@
         <v>35.9</v>
       </c>
       <c r="J4" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L4" t="n">
         <v>8.6</v>
@@ -1058,13 +1125,13 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P4" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R4" t="n">
         <v>8.699999999999999</v>
@@ -1076,7 +1143,7 @@
         <v>38.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
         <v>14.3</v>
@@ -1091,19 +1158,19 @@
         <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA4" t="n">
         <v>20.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1136,13 +1203,13 @@
         <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>29</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
@@ -1163,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1172,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1321,7 +1388,7 @@
         <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1485,7 +1552,7 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
         <v>30</v>
@@ -1497,7 +1564,7 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1700,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
         <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.608</v>
+        <v>0.603</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
@@ -1771,10 +1838,10 @@
         <v>39.6</v>
       </c>
       <c r="J8" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="n">
         <v>8.800000000000001</v>
@@ -1786,28 +1853,28 @@
         <v>0.385</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P8" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
         <v>30.7</v>
       </c>
       <c r="T8" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U8" t="n">
         <v>23.7</v>
       </c>
       <c r="V8" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W8" t="n">
         <v>8.6</v>
@@ -1819,22 +1886,22 @@
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
         <v>20</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.9</v>
+        <v>105.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
         <v>9</v>
@@ -1849,10 +1916,10 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
@@ -1864,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
         <v>23</v>
@@ -1876,16 +1943,16 @@
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>5</v>
@@ -1894,13 +1961,13 @@
         <v>21</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
         <v>10</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2061,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
         <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>0.372</v>
+        <v>0.364</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2138,7 +2205,7 @@
         <v>86.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
@@ -2147,7 +2214,7 @@
         <v>19.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
       <c r="O10" t="n">
         <v>17</v>
@@ -2156,22 +2223,22 @@
         <v>25.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.672</v>
+        <v>0.671</v>
       </c>
       <c r="R10" t="n">
         <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
@@ -2192,10 +2259,10 @@
         <v>100.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,16 +2274,16 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
@@ -2243,7 +2310,7 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
@@ -2264,7 +2331,7 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,13 +2456,13 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>9</v>
@@ -2425,13 +2492,13 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
         <v>14</v>
@@ -2452,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.675</v>
+        <v>0.671</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J12" t="n">
-        <v>80.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L12" t="n">
         <v>9.4</v>
@@ -2511,13 +2578,13 @@
         <v>26.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O12" t="n">
         <v>22</v>
       </c>
       <c r="P12" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0.707</v>
@@ -2526,13 +2593,13 @@
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T12" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U12" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V12" t="n">
         <v>16.3</v>
@@ -2541,7 +2608,7 @@
         <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
@@ -2550,16 +2617,16 @@
         <v>20.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>107.6</v>
+        <v>107.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2577,10 +2644,10 @@
         <v>14</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2604,13 +2671,13 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2753,13 +2820,13 @@
         <v>5</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>20</v>
@@ -2774,7 +2841,7 @@
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>7.1</v>
       </c>
       <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>0.321</v>
+        <v>0.325</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J15" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K15" t="n">
         <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O15" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P15" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
         <v>9.199999999999999</v>
@@ -3075,10 +3142,10 @@
         <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U15" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="V15" t="n">
         <v>15.2</v>
@@ -3090,7 +3157,7 @@
         <v>5.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
         <v>20.1</v>
@@ -3099,13 +3166,13 @@
         <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.9</v>
+        <v>102.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3126,10 +3193,10 @@
         <v>6</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3138,7 +3205,7 @@
         <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3147,19 +3214,19 @@
         <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU15" t="n">
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3177,7 +3244,7 @@
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3332,7 +3399,7 @@
         <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>21</v>
@@ -3341,13 +3408,13 @@
         <v>15</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J17" t="n">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.503</v>
+        <v>0.504</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0.76</v>
@@ -3454,28 +3521,28 @@
         <v>4.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="n">
         <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.8</v>
+        <v>103</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
         <v>4</v>
@@ -3484,7 +3551,7 @@
         <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3529,7 +3596,7 @@
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
@@ -3678,7 +3745,7 @@
         <v>22</v>
       </c>
       <c r="AM18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN18" t="n">
         <v>22</v>
@@ -3699,7 +3766,7 @@
         <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
         <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3773,7 +3840,7 @@
         <v>38.9</v>
       </c>
       <c r="J19" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.445</v>
@@ -3782,7 +3849,7 @@
         <v>7.4</v>
       </c>
       <c r="M19" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N19" t="n">
         <v>0.342</v>
@@ -3791,25 +3858,25 @@
         <v>21.5</v>
       </c>
       <c r="P19" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q19" t="n">
         <v>0.777</v>
       </c>
       <c r="R19" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S19" t="n">
         <v>32.3</v>
       </c>
       <c r="T19" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U19" t="n">
         <v>23.9</v>
       </c>
       <c r="V19" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W19" t="n">
         <v>8.800000000000001</v>
@@ -3821,7 +3888,7 @@
         <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA19" t="n">
         <v>23.4</v>
@@ -3830,25 +3897,25 @@
         <v>106.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
         <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3878,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -3908,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
@@ -4036,7 +4103,7 @@
         <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4066,7 +4133,7 @@
         <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
         <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.727</v>
+        <v>0.724</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4319,7 +4386,7 @@
         <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K22" t="n">
         <v>0.473</v>
@@ -4331,7 +4398,7 @@
         <v>22.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.368</v>
+        <v>0.365</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
@@ -4340,25 +4407,25 @@
         <v>24.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="R22" t="n">
         <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T22" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U22" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
         <v>6.1</v>
@@ -4376,10 +4443,10 @@
         <v>106.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4400,7 +4467,7 @@
         <v>15</v>
       </c>
       <c r="AK22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="n">
         <v>14</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4436,13 +4503,13 @@
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4612,7 +4679,7 @@
         <v>19</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4812,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4943,7 +5010,7 @@
         <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>7</v>
@@ -4964,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -4979,13 +5046,13 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>6</v>
@@ -5128,10 +5195,10 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.346</v>
+        <v>0.351</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J27" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
         <v>6.1</v>
@@ -5241,7 +5308,7 @@
         <v>18.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O27" t="n">
         <v>20.7</v>
@@ -5250,7 +5317,7 @@
         <v>27.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R27" t="n">
         <v>12.1</v>
@@ -5265,7 +5332,7 @@
         <v>18.8</v>
       </c>
       <c r="V27" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W27" t="n">
         <v>7.2</v>
@@ -5283,13 +5350,13 @@
         <v>23.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5310,7 +5377,7 @@
         <v>20</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>28</v>
@@ -5334,7 +5401,7 @@
         <v>6</v>
       </c>
       <c r="AS27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -5343,13 +5410,13 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>25</v>
@@ -5364,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E28" t="n">
         <v>60</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.769</v>
+        <v>0.779</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5414,40 +5481,40 @@
         <v>83</v>
       </c>
       <c r="K28" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.398</v>
+        <v>0.4</v>
       </c>
       <c r="O28" t="n">
         <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.784</v>
+        <v>0.787</v>
       </c>
       <c r="R28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="T28" t="n">
         <v>43.2</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W28" t="n">
         <v>7.4</v>
@@ -5456,22 +5523,22 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA28" t="n">
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.4</v>
+        <v>105.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5513,10 +5580,10 @@
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>13</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5728,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" t="n">
         <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G30" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5787,28 +5854,28 @@
         <v>19.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="O30" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P30" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T30" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V30" t="n">
         <v>14.6</v>
@@ -5823,19 +5890,19 @@
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AA30" t="n">
         <v>20.6</v>
       </c>
-      <c r="AA30" t="n">
-        <v>20.4</v>
-      </c>
       <c r="AB30" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-7.2</v>
+        <v>-7.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5847,7 +5914,7 @@
         <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
         <v>29</v>
@@ -5862,10 +5929,10 @@
         <v>23</v>
       </c>
       <c r="AM30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>23</v>
@@ -5883,7 +5950,7 @@
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
         <v>27</v>
@@ -5904,7 +5971,7 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6032,13 +6099,13 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-8-2013-14</t>
+          <t>2014-04-08</t>
         </is>
       </c>
     </row>
